--- a/front/public/excel/deliverNoteTemplate.xlsx
+++ b/front/public/excel/deliverNoteTemplate.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\b25a0186\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B00B2E-D56C-4E2E-AC8D-DF51C05F4CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C669B5C-2D13-4978-B3F1-635DFCC575F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="納品書" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
